--- a/BaseDeDonnee.xlsx
+++ b/BaseDeDonnee.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="63">
   <si>
     <t>Jours</t>
   </si>
@@ -283,7 +283,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">

--- a/BaseDeDonnee.xlsx
+++ b/BaseDeDonnee.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Jours</t>
   </si>
@@ -105,105 +105,6 @@
   </si>
   <si>
     <t>Muscle</t>
-  </si>
-  <si>
-    <t>Musculation</t>
-  </si>
-  <si>
-    <t>Jambes</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>sgvs</t>
-  </si>
-  <si>
-    <t>Bras</t>
-  </si>
-  <si>
-    <t>Biceps</t>
-  </si>
-  <si>
-    <t>senace</t>
-  </si>
-  <si>
-    <t>Nom de votre séance</t>
-  </si>
-  <si>
-    <t>Exercices</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>kiki</t>
-  </si>
-  <si>
-    <t>29/12/2023</t>
-  </si>
-  <si>
-    <t>11:43:27</t>
-  </si>
-  <si>
-    <t>11:45:07</t>
-  </si>
-  <si>
-    <t>culr</t>
-  </si>
-  <si>
-    <t>dc</t>
-  </si>
-  <si>
-    <t>Pectoraux</t>
-  </si>
-  <si>
-    <t>Haut</t>
-  </si>
-  <si>
-    <t>squat</t>
-  </si>
-  <si>
-    <t>Fessier</t>
-  </si>
-  <si>
-    <t>curl mateau</t>
-  </si>
-  <si>
-    <t>12:15:36</t>
-  </si>
-  <si>
-    <t>bras</t>
-  </si>
-  <si>
-    <t>tesr</t>
-  </si>
-  <si>
-    <t>12:20:14</t>
-  </si>
-  <si>
-    <t>poulie</t>
-  </si>
-  <si>
-    <t>Dos</t>
-  </si>
-  <si>
-    <t>Trapèze</t>
-  </si>
-  <si>
-    <t>Epaules</t>
-  </si>
-  <si>
-    <t>Antérieur</t>
-  </si>
-  <si>
-    <t>curl</t>
-  </si>
-  <si>
-    <t>31/12/2023</t>
-  </si>
-  <si>
-    <t>19:06:07</t>
   </si>
 </sst>
 </file>
@@ -274,25 +175,16 @@
       <c r="A3" t="s" s="1">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="1">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="1">
@@ -303,9 +195,6 @@
       <c r="A7" t="s" s="1">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="1">
@@ -319,7 +208,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -360,40 +249,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" t="s">
-        <v>44</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -401,7 +256,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -424,26 +279,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -451,7 +286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -468,76 +303,6 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/BaseDeDonnee.xlsx
+++ b/BaseDeDonnee.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>Jours</t>
   </si>
@@ -105,6 +105,93 @@
   </si>
   <si>
     <t>Muscle</t>
+  </si>
+  <si>
+    <t>Pompes</t>
+  </si>
+  <si>
+    <t>Conditionnement</t>
+  </si>
+  <si>
+    <t>Pectoraux</t>
+  </si>
+  <si>
+    <t>Suppérieur</t>
+  </si>
+  <si>
+    <t>Squats</t>
+  </si>
+  <si>
+    <t>Musculation</t>
+  </si>
+  <si>
+    <t>Jambes</t>
+  </si>
+  <si>
+    <t>Quadriceps</t>
+  </si>
+  <si>
+    <t>Curl</t>
+  </si>
+  <si>
+    <t>Bras</t>
+  </si>
+  <si>
+    <t>Biceps</t>
+  </si>
+  <si>
+    <t>Tractions</t>
+  </si>
+  <si>
+    <t>Dos</t>
+  </si>
+  <si>
+    <t>Grand dorsale</t>
+  </si>
+  <si>
+    <t>Dips</t>
+  </si>
+  <si>
+    <t>Tricpes</t>
+  </si>
+  <si>
+    <t>Rowing barre</t>
+  </si>
+  <si>
+    <t>Soulevé de terre</t>
+  </si>
+  <si>
+    <t>Presse</t>
+  </si>
+  <si>
+    <t>Leg curl</t>
+  </si>
+  <si>
+    <t>Ischio</t>
+  </si>
+  <si>
+    <t>Développé militaire</t>
+  </si>
+  <si>
+    <t>Epaules</t>
+  </si>
+  <si>
+    <t>Latérale</t>
+  </si>
+  <si>
+    <t>Shrug</t>
+  </si>
+  <si>
+    <t>Trapèze</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Abdominaux</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -180,6 +267,9 @@
       <c r="A4" t="s" s="1">
         <v>4</v>
       </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="1">
@@ -208,7 +298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -247,6 +337,17 @@
       </c>
       <c r="L1" t="s" s="1">
         <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -286,21 +387,189 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
